--- a/Тест2/255.xlsx
+++ b/Тест2/255.xlsx
@@ -273,7 +273,7 @@
     <t xml:space="preserve">Bijg'itish usulida natija qanday hisoblanadi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Mikroskopda hujayralarni sanab hisoblanadi</t>
+    <t xml:space="preserve">Mikroskopda hujayralar sanalib hisoblanadi</t>
   </si>
   <si>
     <t xml:space="preserve">Hamma naychalar o'rtachasi olinib hisoblanadi</t>
@@ -282,13 +282,13 @@
     <t xml:space="preserve">Koloniyalar og'irligini o'lchab hisoblanadi</t>
   </si>
   <si>
-    <t xml:space="preserve">Bitta naycha natijasini ikki barobar oshirib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naychalar kombinatsiyasi bo'yicha ehtimoliy son jadvalidan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To'g'ri javob: Naychalar kombinatsiyasi bo'yicha ehtimoliy son jadvalidan. Ijobiy va manfiy naychalarning kombinatsiyasiga mos eng ehtimoliy son jadvaldan olinadi. Manba: Mavzu materiali (255.docx); WHO. Guidelines for drinking-water quality, 4-nashr, 1-ilova bilan (2017).</t>
+    <t xml:space="preserve">Bitta naycha natijasi ikki barobar oshiriladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naychalar kombinatsiyasi bo'yicha EHS jadvalidan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To'g'ri javob: Naychalar kombinatsiyasi bo'yicha EHS jadvalidan. Ijobiy va manfiy naychalarning kombinatsiyasiga mos eng ehtimoliy son jadvaldan olinadi. Manba: Mavzu materiali (255.docx); WHO. Guidelines for drinking-water quality, 4-nashr, 1-ilova bilan (2017).</t>
   </si>
 </sst>
 </file>
